--- a/data/trans_orig/Q5419_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar medios de transporte en 2023</t>
+          <t>Población según si es capaz de usar medios de transporte en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36773</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50085</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34902</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107361</t>
+          <t>106860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123000</t>
+          <t>123164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>99927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115545</t>
+          <t>116118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210466</t>
+          <t>209974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234517</t>
+          <t>233288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26975</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43547</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122915</t>
+          <t>122305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138239</t>
+          <t>137514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142727</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161556</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270137</t>
+          <t>268989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294070</t>
+          <t>293409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,62%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44309</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>27941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115038</t>
+          <t>115377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126778</t>
+          <t>128159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247471</t>
+          <t>248683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348306</t>
+          <t>348231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388223</t>
+          <t>387614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475697</t>
+          <t>474507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27666</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29549</t>
+          <t>29702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>40586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172237</t>
+          <t>171562</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186747</t>
+          <t>186794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188349</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209660</t>
+          <t>209909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365790</t>
+          <t>366174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>392767</t>
+          <t>393745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114085</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>149081</t>
+          <t>150246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54610</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87168</t>
+          <t>86249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>108177</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>96310</t>
+          <t>96229</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>122987</t>
+          <t>124225</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>532689</t>
+          <t>531928</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>561799</t>
+          <t>560778</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>702283</t>
+          <t>702232</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>892974</t>
+          <t>913384</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1261608</t>
+          <t>1263708</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1455890</t>
+          <t>1439393</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5419_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43961</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33755</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22263</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>37590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>114933</t>
+          <t>128066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106860</t>
+          <t>118763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123164</t>
+          <t>135669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>107963</t>
+          <t>114983</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99927</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116118</t>
+          <t>124235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>222896</t>
+          <t>243049</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209974</t>
+          <t>229984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233288</t>
+          <t>255934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30428</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>28787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42808</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130596</t>
+          <t>146900</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122305</t>
+          <t>137665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137514</t>
+          <t>154755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>151836</t>
+          <t>167788</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142747</t>
+          <t>156949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160565</t>
+          <t>177629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>282433</t>
+          <t>314687</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>268989</t>
+          <t>301399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293409</t>
+          <t>327492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217876</t>
+          <t>241105</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217876</t>
+          <t>241105</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217876</t>
+          <t>241105</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419308</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419308</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419308</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122073</t>
+          <t>143035</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115377</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128159</t>
+          <t>148790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>314355</t>
+          <t>124527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248683</t>
+          <t>114856</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348231</t>
+          <t>133186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>436428</t>
+          <t>267562</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>387614</t>
+          <t>254362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>474507</t>
+          <t>279183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>38146</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>47344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29702</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23827</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>35378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>34065</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>180138</t>
+          <t>189886</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171562</t>
+          <t>181402</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186794</t>
+          <t>196496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>199327</t>
+          <t>212257</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188139</t>
+          <t>199488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209909</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>379466</t>
+          <t>402142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366174</t>
+          <t>385877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393745</t>
+          <t>416811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>51922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>96110</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>83400</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116320</t>
+          <t>109932</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>120194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>65888</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86249</t>
+          <t>85837</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>96225</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>108177</t>
+          <t>112258</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>81303</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>69719</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>96229</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>102658</t>
+          <t>111754</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>124225</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>547740</t>
+          <t>607887</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>531928</t>
+          <t>591632</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>560778</t>
+          <t>622981</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>773482</t>
+          <t>619555</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>702232</t>
+          <t>596836</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>913384</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1321222</t>
+          <t>1227442</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1263708</t>
+          <t>1201172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1439393</t>
+          <t>1254667</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
